--- a/Design Files/Solenoid-Switching-Board-v1.0/BOM/eSpark-BOM-Solenoid-Switching-Board-v1.0.xlsx
+++ b/Design Files/Solenoid-Switching-Board-v1.0/BOM/eSpark-BOM-Solenoid-Switching-Board-v1.0.xlsx
@@ -12,14 +12,14 @@
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="145">
   <si>
     <t>Component list</t>
   </si>
@@ -129,9 +129,6 @@
     <t>CAP CER 0.1UF 50V X5R 0603</t>
   </si>
   <si>
-    <t>CAP ALUM 220UF 20% 50V SMD</t>
-  </si>
-  <si>
     <t>SMC(DO-214AB) Diodes - Fast Recovery Rectifiers ROHS</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
     <t>Cap-0603</t>
   </si>
   <si>
-    <t>UCD-220uF-10mmDia</t>
-  </si>
-  <si>
     <t>SMC</t>
   </si>
   <si>
@@ -210,9 +204,6 @@
     <t>CC0603KRX5R9BB104</t>
   </si>
   <si>
-    <t>UCD1H221MNL1GS</t>
-  </si>
-  <si>
     <t>MURS360T3G</t>
   </si>
   <si>
@@ -252,9 +243,6 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>Nichicon</t>
-  </si>
-  <si>
     <t>FUXINSEMI</t>
   </si>
   <si>
@@ -285,9 +273,6 @@
     <t>C110022</t>
   </si>
   <si>
-    <t>C116211</t>
-  </si>
-  <si>
     <t>C7436549</t>
   </si>
   <si>
@@ -327,9 +312,6 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>220uF</t>
-  </si>
-  <si>
     <t>2.2K</t>
   </si>
   <si>
@@ -396,9 +378,6 @@
     <t>0.0028</t>
   </si>
   <si>
-    <t>0.2931</t>
-  </si>
-  <si>
     <t>0.1245</t>
   </si>
   <si>
@@ -442,6 +421,39 @@
   </si>
   <si>
     <t>-----</t>
+  </si>
+  <si>
+    <t>100uF 50V ±20% SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>RVT1H101M0607</t>
+  </si>
+  <si>
+    <t>ROQANG</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>C3151829</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 60V 5A SMA</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>SS56</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>C65009</t>
   </si>
 </sst>
 </file>
@@ -783,7 +795,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -897,6 +909,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -909,9 +924,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1202,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1235,14 +1250,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1253,7 +1268,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -1277,7 +1292,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -1367,43 +1382,43 @@
         <v>33</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q7" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1422,22 +1437,22 @@
         <v>34</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>140</v>
+        <v>72</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L8" s="14">
         <v>4</v>
@@ -1449,11 +1464,11 @@
       <c r="N8" s="20">
         <v>21</v>
       </c>
-      <c r="O8" s="48" t="s">
-        <v>121</v>
+      <c r="O8" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="Q8" s="15">
         <f>P8*N8</f>
@@ -1464,7 +1479,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B23" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B24" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1477,22 +1492,22 @@
         <v>35</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="49" t="s">
-        <v>140</v>
+        <v>73</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K9" s="43" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L9" s="20">
         <v>9</v>
@@ -1502,13 +1517,13 @@
         <v>45</v>
       </c>
       <c r="N9" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="O9" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="O9" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="P9" s="15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="Q9" s="21">
         <f t="shared" ref="Q9" si="2">P9*N9</f>
@@ -1516,7 +1531,7 @@
       </c>
       <c r="R9" s="20"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="16">
         <f>ROW(B10) - ROW($B$7)</f>
@@ -1528,26 +1543,26 @@
       <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>36</v>
+      <c r="E10" s="42" t="s">
+        <v>134</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>63</v>
+        <v>113</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>135</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>140</v>
+        <v>136</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="L10" s="14">
         <v>1</v>
@@ -1559,15 +1574,15 @@
       <c r="N10" s="20">
         <v>10</v>
       </c>
-      <c r="O10" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>125</v>
+      <c r="O10" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P10" s="15">
+        <v>5.96E-2</v>
       </c>
       <c r="Q10" s="15">
         <f>P10*N10</f>
-        <v>2.931</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="R10" s="14"/>
     </row>
@@ -1584,25 +1599,25 @@
         <v>20</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="49" t="s">
-        <v>140</v>
+        <v>74</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="L11" s="20">
         <v>4</v>
@@ -1614,11 +1629,11 @@
       <c r="N11" s="20">
         <v>25</v>
       </c>
-      <c r="O11" s="48" t="s">
-        <v>121</v>
+      <c r="O11" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="P11" s="15" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="Q11" s="21">
         <f t="shared" ref="Q11" si="4">P11*N11</f>
@@ -1639,25 +1654,25 @@
         <v>21</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="49" t="s">
-        <v>140</v>
+      <c r="I12" s="45" t="s">
+        <v>133</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -1670,10 +1685,10 @@
         <v>10</v>
       </c>
       <c r="O12" s="44" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Q12" s="15">
         <f>P12*N12</f>
@@ -1681,635 +1696,665 @@
       </c>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18" ht="48" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
+        <f>ROW(B13) - ROW($B$7)</f>
+        <v>6</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="14">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14">
+        <f>L13*5</f>
+        <v>5</v>
+      </c>
+      <c r="N13" s="20">
+        <v>10</v>
+      </c>
+      <c r="O13" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="P13" s="15">
+        <v>4.53E-2</v>
+      </c>
+      <c r="Q13" s="15">
+        <f>P13*N13</f>
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="R13" s="14"/>
+    </row>
+    <row r="14" spans="1:18" ht="48" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="17">
         <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="20">
+        <v>4</v>
+      </c>
+      <c r="M14" s="20">
+        <f t="shared" ref="M14" si="5">L14*5</f>
+        <v>20</v>
+      </c>
+      <c r="N14" s="20">
+        <v>25</v>
+      </c>
+      <c r="O14" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q14" s="21">
+        <f t="shared" ref="Q14" si="6">P14*N14</f>
+        <v>4.7225000000000001</v>
+      </c>
+      <c r="R14" s="20"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="16">
+        <f>ROW(B15) - ROW($B$7)</f>
+        <v>8</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" s="14">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
+        <f>L15*5</f>
+        <v>5</v>
+      </c>
+      <c r="N15" s="20">
         <v>6</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="O15" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q15" s="15">
+        <f>P15*N15</f>
+        <v>7.8431999999999995</v>
+      </c>
+      <c r="R15" s="14"/>
+    </row>
+    <row r="16" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="17">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L13" s="20">
-        <v>4</v>
-      </c>
-      <c r="M13" s="20">
-        <f t="shared" ref="M13" si="5">L13*5</f>
-        <v>20</v>
-      </c>
-      <c r="N13" s="20">
+      <c r="C16" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L16" s="20">
+        <v>1</v>
+      </c>
+      <c r="M16" s="20">
+        <f t="shared" ref="M16" si="7">L16*5</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="20">
+        <v>10</v>
+      </c>
+      <c r="O16" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="21">
+        <f t="shared" ref="Q16" si="8">P16*N16</f>
+        <v>0.69000000000000006</v>
+      </c>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="16">
+        <f>ROW(B17) - ROW($B$7)</f>
+        <v>10</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="O13" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q13" s="21">
-        <f t="shared" ref="Q13" si="6">P13*N13</f>
-        <v>4.7225000000000001</v>
-      </c>
-      <c r="R13" s="20"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="16">
-        <f>ROW(B14) - ROW($B$7)</f>
-        <v>7</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="K14" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="E17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="14">
+        <v>1715721</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="14">
         <v>1</v>
       </c>
-      <c r="M14" s="14">
-        <f>L14*5</f>
+      <c r="M17" s="14">
+        <f>L17*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N17" s="14">
         <v>6</v>
       </c>
-      <c r="O14" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q14" s="15">
-        <f>P14*N14</f>
-        <v>7.8431999999999995</v>
-      </c>
-      <c r="R14" s="14"/>
-    </row>
-    <row r="15" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="17">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="20">
-        <v>1</v>
-      </c>
-      <c r="M15" s="20">
-        <f t="shared" ref="M15" si="7">L15*5</f>
-        <v>5</v>
-      </c>
-      <c r="N15" s="20">
-        <v>10</v>
-      </c>
-      <c r="O15" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q15" s="21">
-        <f t="shared" ref="Q15" si="8">P15*N15</f>
-        <v>0.69000000000000006</v>
-      </c>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="16">
-        <f>ROW(B16) - ROW($B$7)</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1715721</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="K16" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L16" s="14">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14">
-        <f>L16*5</f>
-        <v>5</v>
-      </c>
-      <c r="N16" s="14">
-        <v>6</v>
-      </c>
-      <c r="O16" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="P16" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q16" s="15">
-        <f>P16*N16</f>
+      <c r="O17" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q17" s="15">
+        <f>P17*N17</f>
         <v>2.3418000000000001</v>
       </c>
-      <c r="R16" s="14"/>
-    </row>
-    <row r="17" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="17">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L17" s="20">
-        <v>4</v>
-      </c>
-      <c r="M17" s="20">
-        <f t="shared" ref="M17" si="9">L17*5</f>
-        <v>20</v>
-      </c>
-      <c r="N17" s="20">
-        <v>40</v>
-      </c>
-      <c r="O17" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q17" s="21">
-        <f t="shared" ref="Q17" si="10">P17*N17</f>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="R17" s="20"/>
+      <c r="R17" s="14"/>
     </row>
     <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="16">
-        <f>ROW(B18) - ROW($B$7)</f>
+      <c r="B18" s="17">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="20">
+        <v>4</v>
+      </c>
+      <c r="M18" s="20">
+        <f t="shared" ref="M18" si="9">L18*5</f>
+        <v>20</v>
+      </c>
+      <c r="N18" s="20">
+        <v>40</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q18" s="21">
+        <f t="shared" ref="Q18" si="10">P18*N18</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="R18" s="20"/>
+    </row>
+    <row r="19" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="16">
+        <f>ROW(B19) - ROW($B$7)</f>
+        <v>12</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K18" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L18" s="14">
+      <c r="E19" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="14">
         <v>5</v>
       </c>
-      <c r="M18" s="14">
-        <f>L18*5</f>
+      <c r="M19" s="14">
+        <f>L19*5</f>
         <v>25</v>
       </c>
-      <c r="N18" s="20" t="s">
+      <c r="N19" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P19" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="O18" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q18" s="15">
-        <f>P18*N18</f>
+      <c r="Q19" s="15">
+        <f>P19*N19</f>
         <v>0.90800000000000003</v>
       </c>
-      <c r="R18" s="14"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="17">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="L19" s="20">
-        <v>4</v>
-      </c>
-      <c r="M19" s="20">
-        <f t="shared" ref="M19" si="11">L19*5</f>
-        <v>20</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="O19" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P19" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q19" s="21">
-        <f t="shared" ref="Q19" si="12">P19*N19</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R19" s="20"/>
+      <c r="R19" s="14"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="16">
-        <f>ROW(B20) - ROW($B$7)</f>
+      <c r="B20" s="17">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="L20" s="14">
+      <c r="D20" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="K20" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" s="20">
         <v>4</v>
       </c>
-      <c r="M20" s="14">
-        <f>L20*5</f>
+      <c r="M20" s="20">
+        <f t="shared" ref="M20" si="11">L20*5</f>
         <v>20</v>
       </c>
       <c r="N20" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="O20" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="O20" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="P20" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q20" s="15">
-        <f>P20*N20</f>
-        <v>0.05</v>
-      </c>
-      <c r="R20" s="14"/>
+        <v>129</v>
+      </c>
+      <c r="Q20" s="21">
+        <f t="shared" ref="Q20" si="12">P20*N20</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R20" s="20"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="17">
-        <f t="shared" si="0"/>
+      <c r="B21" s="16">
+        <f>ROW(B21) - ROW($B$7)</f>
         <v>14</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J21" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="L21" s="20">
-        <v>8</v>
-      </c>
-      <c r="M21" s="20">
-        <f t="shared" ref="M21" si="13">L21*5</f>
-        <v>40</v>
+      <c r="D21" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="14">
+        <v>4</v>
+      </c>
+      <c r="M21" s="14">
+        <f>L21*5</f>
+        <v>20</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="O21" s="48" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="O21" s="44" t="s">
+        <v>115</v>
       </c>
       <c r="P21" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q21" s="21">
-        <f t="shared" ref="Q21" si="14">P21*N21</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R21" s="20"/>
+        <v>130</v>
+      </c>
+      <c r="Q21" s="15">
+        <f>P21*N21</f>
+        <v>0.05</v>
+      </c>
+      <c r="R21" s="14"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="16">
-        <f>ROW(B22) - ROW($B$7)</f>
+      <c r="B22" s="17">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="20">
+        <v>8</v>
+      </c>
+      <c r="M22" s="20">
+        <f t="shared" ref="M22" si="13">L22*5</f>
+        <v>40</v>
+      </c>
+      <c r="N22" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="O22" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q22" s="21">
+        <f t="shared" ref="Q22" si="14">P22*N22</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R22" s="20"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="16">
+        <f>ROW(B23) - ROW($B$7)</f>
+        <v>16</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E23" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="K23" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" s="14">
+        <v>5</v>
+      </c>
+      <c r="M23" s="14">
+        <f>L23*5</f>
+        <v>25</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="P23" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q23" s="15">
+        <f>P23*N23</f>
+        <v>0.06</v>
+      </c>
+      <c r="R23" s="14"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="17">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="L22" s="14">
-        <v>5</v>
-      </c>
-      <c r="M22" s="14">
-        <f>L22*5</f>
-        <v>25</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="O22" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="P22" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q22" s="15">
-        <f>P22*N22</f>
-        <v>0.06</v>
-      </c>
-      <c r="R22" s="14"/>
-    </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="17">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="K23" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L23" s="20">
+      <c r="F24" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L24" s="20">
         <v>4</v>
       </c>
-      <c r="M23" s="20">
-        <f t="shared" ref="M23" si="15">L23*5</f>
+      <c r="M24" s="20">
+        <f t="shared" ref="M24" si="15">L24*5</f>
         <v>20</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N24" s="20">
         <v>21</v>
       </c>
-      <c r="O23" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="P23" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q23" s="21">
-        <f t="shared" ref="Q23" si="16">P23*N23</f>
+      <c r="O24" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="P24" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q24" s="21">
+        <f t="shared" ref="Q24" si="16">P24*N24</f>
         <v>86.39609999999999</v>
       </c>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="18">
-        <f>SUM(Q8:Q23)</f>
-        <v>124.49159999999999</v>
-      </c>
-      <c r="R24" s="1"/>
+      <c r="R24" s="20"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2325,45 +2370,71 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="46" t="s">
+      <c r="N25" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="18">
+        <f>SUM(Q8:Q24)</f>
+        <v>122.6096</v>
+      </c>
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="O25" s="47"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="19">
-        <f>Q24/5</f>
-        <v>24.898319999999998</v>
-      </c>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="37" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M37" s="38"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="19">
+        <f>Q25/5</f>
+        <v>24.521920000000001</v>
+      </c>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="38" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M38" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N24:P24"/>
     <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O12" r:id="rId1"/>
-    <hyperlink ref="O16" r:id="rId2"/>
-    <hyperlink ref="O17" r:id="rId3"/>
-    <hyperlink ref="O20" r:id="rId4"/>
-    <hyperlink ref="O22" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId2"/>
+    <hyperlink ref="O18" r:id="rId3"/>
+    <hyperlink ref="O21" r:id="rId4"/>
+    <hyperlink ref="O23" r:id="rId5"/>
     <hyperlink ref="O8" r:id="rId6"/>
     <hyperlink ref="O9" r:id="rId7"/>
-    <hyperlink ref="O10" r:id="rId8"/>
-    <hyperlink ref="O11" r:id="rId9"/>
-    <hyperlink ref="O13" r:id="rId10"/>
-    <hyperlink ref="O14" r:id="rId11"/>
-    <hyperlink ref="O15" r:id="rId12"/>
-    <hyperlink ref="O18" r:id="rId13"/>
-    <hyperlink ref="O19" r:id="rId14"/>
-    <hyperlink ref="O21" r:id="rId15"/>
-    <hyperlink ref="O23" r:id="rId16"/>
+    <hyperlink ref="O11" r:id="rId8"/>
+    <hyperlink ref="O14" r:id="rId9"/>
+    <hyperlink ref="O15" r:id="rId10"/>
+    <hyperlink ref="O16" r:id="rId11"/>
+    <hyperlink ref="O19" r:id="rId12"/>
+    <hyperlink ref="O20" r:id="rId13"/>
+    <hyperlink ref="O22" r:id="rId14"/>
+    <hyperlink ref="O24" r:id="rId15"/>
+    <hyperlink ref="O10" r:id="rId16"/>
+    <hyperlink ref="O13" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/Design Files/Solenoid-Switching-Board-v1.0/BOM/eSpark-BOM-Solenoid-Switching-Board-v1.0.xlsx
+++ b/Design Files/Solenoid-Switching-Board-v1.0/BOM/eSpark-BOM-Solenoid-Switching-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="151">
   <si>
     <t>Component list</t>
   </si>
@@ -454,6 +454,24 @@
   </si>
   <si>
     <t>C65009</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 1A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287001.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>C142679</t>
   </si>
 </sst>
 </file>
@@ -912,6 +930,12 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -922,12 +946,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1217,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1250,14 +1268,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1464,7 +1482,7 @@
       <c r="N8" s="20">
         <v>21</v>
       </c>
-      <c r="O8" s="49" t="s">
+      <c r="O8" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P8" s="15" t="s">
@@ -1479,7 +1497,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B24" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B25" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1519,7 +1537,7 @@
       <c r="N9" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="O9" s="49" t="s">
+      <c r="O9" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P9" s="15" t="s">
@@ -1574,7 +1592,7 @@
       <c r="N10" s="20">
         <v>10</v>
       </c>
-      <c r="O10" s="49" t="s">
+      <c r="O10" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P10" s="15">
@@ -1629,7 +1647,7 @@
       <c r="N11" s="20">
         <v>25</v>
       </c>
-      <c r="O11" s="49" t="s">
+      <c r="O11" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P11" s="15" t="s">
@@ -1739,7 +1757,7 @@
       <c r="N13" s="20">
         <v>10</v>
       </c>
-      <c r="O13" s="50" t="s">
+      <c r="O13" s="47" t="s">
         <v>115</v>
       </c>
       <c r="P13" s="15">
@@ -1794,7 +1812,7 @@
       <c r="N14" s="20">
         <v>25</v>
       </c>
-      <c r="O14" s="49" t="s">
+      <c r="O14" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P14" s="15" t="s">
@@ -1849,7 +1867,7 @@
       <c r="N15" s="20">
         <v>6</v>
       </c>
-      <c r="O15" s="49" t="s">
+      <c r="O15" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P15" s="15" t="s">
@@ -1904,7 +1922,7 @@
       <c r="N16" s="20">
         <v>10</v>
       </c>
-      <c r="O16" s="49" t="s">
+      <c r="O16" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="15" t="s">
@@ -2069,7 +2087,7 @@
       <c r="N19" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="O19" s="49" t="s">
+      <c r="O19" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P19" s="15" t="s">
@@ -2124,7 +2142,7 @@
       <c r="N20" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="49" t="s">
+      <c r="O20" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P20" s="15" t="s">
@@ -2234,7 +2252,7 @@
       <c r="N22" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="O22" s="49" t="s">
+      <c r="O22" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P22" s="15" t="s">
@@ -2301,10 +2319,10 @@
       </c>
       <c r="R23" s="14"/>
     </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="17">
-        <f t="shared" si="0"/>
+      <c r="B24" s="16">
+        <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -2338,48 +2356,78 @@
         <v>4</v>
       </c>
       <c r="M24" s="20">
-        <f t="shared" ref="M24" si="15">L24*5</f>
+        <f t="shared" ref="M24:M25" si="15">L24*5</f>
         <v>20</v>
       </c>
       <c r="N24" s="20">
         <v>21</v>
       </c>
-      <c r="O24" s="49" t="s">
+      <c r="O24" s="46" t="s">
         <v>115</v>
       </c>
       <c r="P24" s="15" t="s">
         <v>132</v>
       </c>
       <c r="Q24" s="21">
-        <f t="shared" ref="Q24" si="16">P24*N24</f>
+        <f t="shared" ref="Q24:Q25" si="16">P24*N24</f>
         <v>86.39609999999999</v>
       </c>
       <c r="R24" s="20"/>
     </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="47" t="s">
-        <v>3</v>
-      </c>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="18">
-        <f>SUM(Q8:Q24)</f>
-        <v>122.6096</v>
-      </c>
-      <c r="R25" s="1"/>
+      <c r="B25" s="17">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L25" s="20">
+        <v>1</v>
+      </c>
+      <c r="M25" s="20">
+        <f t="shared" si="15"/>
+        <v>5</v>
+      </c>
+      <c r="N25" s="20">
+        <v>5</v>
+      </c>
+      <c r="O25" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="P25" s="15">
+        <v>8.8800000000000004E-2</v>
+      </c>
+      <c r="Q25" s="21">
+        <f t="shared" si="16"/>
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="R25" s="20"/>
     </row>
     <row r="26" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -2395,25 +2443,50 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="47" t="s">
+      <c r="N26" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="50"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="18">
+        <f>SUM(Q8:Q25)</f>
+        <v>123.0536</v>
+      </c>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="19">
-        <f>Q25/5</f>
-        <v>24.521920000000001</v>
-      </c>
-      <c r="R26" s="1"/>
-    </row>
-    <row r="38" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M38" s="38"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="19">
+        <f>Q26/5</f>
+        <v>24.610720000000001</v>
+      </c>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="39" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M39" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N25:P25"/>
     <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N27:P27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O12" r:id="rId1"/>
@@ -2433,8 +2506,9 @@
     <hyperlink ref="O24" r:id="rId15"/>
     <hyperlink ref="O10" r:id="rId16"/>
     <hyperlink ref="O13" r:id="rId17"/>
+    <hyperlink ref="O25" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>